--- a/AAII_Financials/Quarterly/INEO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INEO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
   <si>
     <t>INEO</t>
   </si>
@@ -742,10 +742,10 @@
         <v>15400</v>
       </c>
       <c r="H8" s="3">
-        <v>15200</v>
+        <v>17400</v>
       </c>
       <c r="I8" s="3">
-        <v>15200</v>
+        <v>17400</v>
       </c>
       <c r="J8" s="3">
         <v>14000</v>
@@ -783,10 +783,10 @@
         <v>12400</v>
       </c>
       <c r="H9" s="3">
-        <v>12700</v>
+        <v>14200</v>
       </c>
       <c r="I9" s="3">
-        <v>12700</v>
+        <v>14200</v>
       </c>
       <c r="J9" s="3">
         <v>11100</v>
@@ -824,10 +824,10 @@
         <v>3000</v>
       </c>
       <c r="H10" s="3">
-        <v>2600</v>
+        <v>3300</v>
       </c>
       <c r="I10" s="3">
-        <v>2600</v>
+        <v>3300</v>
       </c>
       <c r="J10" s="3">
         <v>2900</v>
@@ -1060,10 +1060,10 @@
         <v>14800</v>
       </c>
       <c r="H17" s="3">
-        <v>15700</v>
+        <v>17700</v>
       </c>
       <c r="I17" s="3">
-        <v>15700</v>
+        <v>17700</v>
       </c>
       <c r="J17" s="3">
         <v>13100</v>
@@ -1101,10 +1101,10 @@
         <v>600</v>
       </c>
       <c r="H18" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="I18" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="J18" s="3">
         <v>900</v>
@@ -1159,10 +1159,10 @@
         <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
         <v>-300</v>
@@ -1200,10 +1200,10 @@
         <v>600</v>
       </c>
       <c r="H21" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="I21" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="J21" s="3">
         <v>1200</v>
@@ -1241,10 +1241,10 @@
         <v>400</v>
       </c>
       <c r="H22" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I22" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="J22" s="3">
         <v>300</v>
@@ -1282,10 +1282,10 @@
         <v>200</v>
       </c>
       <c r="H23" s="3">
-        <v>-800</v>
+        <v>-600</v>
       </c>
       <c r="I23" s="3">
-        <v>-800</v>
+        <v>-600</v>
       </c>
       <c r="J23" s="3">
         <v>900</v>
@@ -1405,10 +1405,10 @@
         <v>100</v>
       </c>
       <c r="H26" s="3">
-        <v>-800</v>
+        <v>-700</v>
       </c>
       <c r="I26" s="3">
-        <v>-800</v>
+        <v>-700</v>
       </c>
       <c r="J26" s="3">
         <v>800</v>
@@ -1446,10 +1446,10 @@
         <v>100</v>
       </c>
       <c r="H27" s="3">
-        <v>-800</v>
+        <v>-700</v>
       </c>
       <c r="I27" s="3">
-        <v>-800</v>
+        <v>-700</v>
       </c>
       <c r="J27" s="3">
         <v>800</v>
@@ -1651,10 +1651,10 @@
         <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
         <v>300</v>
@@ -1692,10 +1692,10 @@
         <v>100</v>
       </c>
       <c r="H33" s="3">
-        <v>-800</v>
+        <v>-700</v>
       </c>
       <c r="I33" s="3">
-        <v>-800</v>
+        <v>-700</v>
       </c>
       <c r="J33" s="3">
         <v>800</v>
@@ -1774,10 +1774,10 @@
         <v>100</v>
       </c>
       <c r="H35" s="3">
-        <v>-800</v>
+        <v>-700</v>
       </c>
       <c r="I35" s="3">
-        <v>-800</v>
+        <v>-700</v>
       </c>
       <c r="J35" s="3">
         <v>800</v>
@@ -1895,10 +1895,10 @@
         <v>2100</v>
       </c>
       <c r="H41" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="I41" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="J41" s="3">
         <v>800</v>
@@ -1936,10 +1936,10 @@
         <v>6300</v>
       </c>
       <c r="H42" s="3">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="I42" s="3">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="J42" s="3">
         <v>2800</v>
@@ -1977,10 +1977,10 @@
         <v>15600</v>
       </c>
       <c r="H43" s="3">
-        <v>13200</v>
+        <v>16000</v>
       </c>
       <c r="I43" s="3">
-        <v>13200</v>
+        <v>16000</v>
       </c>
       <c r="J43" s="3">
         <v>16100</v>
@@ -2018,10 +2018,10 @@
         <v>18200</v>
       </c>
       <c r="H44" s="3">
-        <v>18100</v>
+        <v>19400</v>
       </c>
       <c r="I44" s="3">
-        <v>18100</v>
+        <v>19400</v>
       </c>
       <c r="J44" s="3">
         <v>17400</v>
@@ -2100,10 +2100,10 @@
         <v>42500</v>
       </c>
       <c r="H46" s="3">
-        <v>36800</v>
+        <v>41300</v>
       </c>
       <c r="I46" s="3">
-        <v>36800</v>
+        <v>41300</v>
       </c>
       <c r="J46" s="3">
         <v>37400</v>
@@ -2182,10 +2182,10 @@
         <v>3200</v>
       </c>
       <c r="H48" s="3">
-        <v>1700</v>
+        <v>3100</v>
       </c>
       <c r="I48" s="3">
-        <v>1700</v>
+        <v>3100</v>
       </c>
       <c r="J48" s="3">
         <v>2200</v>
@@ -2345,11 +2345,11 @@
       <c r="G52" s="3">
         <v>1200</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
+      <c r="H52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1300</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>8</v>
@@ -2428,10 +2428,10 @@
         <v>52600</v>
       </c>
       <c r="H54" s="3">
-        <v>39600</v>
+        <v>45800</v>
       </c>
       <c r="I54" s="3">
-        <v>39600</v>
+        <v>45800</v>
       </c>
       <c r="J54" s="3">
         <v>39600</v>
@@ -2503,10 +2503,10 @@
         <v>5200</v>
       </c>
       <c r="H57" s="3">
-        <v>4600</v>
+        <v>4900</v>
       </c>
       <c r="I57" s="3">
-        <v>4600</v>
+        <v>4900</v>
       </c>
       <c r="J57" s="3">
         <v>4100</v>
@@ -2544,10 +2544,10 @@
         <v>19200</v>
       </c>
       <c r="H58" s="3">
-        <v>18300</v>
+        <v>19600</v>
       </c>
       <c r="I58" s="3">
-        <v>18300</v>
+        <v>19600</v>
       </c>
       <c r="J58" s="3">
         <v>17900</v>
@@ -2585,10 +2585,10 @@
         <v>13200</v>
       </c>
       <c r="H59" s="3">
-        <v>5600</v>
+        <v>12500</v>
       </c>
       <c r="I59" s="3">
-        <v>5600</v>
+        <v>12500</v>
       </c>
       <c r="J59" s="3">
         <v>13500</v>
@@ -2626,10 +2626,10 @@
         <v>37600</v>
       </c>
       <c r="H60" s="3">
-        <v>28600</v>
+        <v>37000</v>
       </c>
       <c r="I60" s="3">
-        <v>28600</v>
+        <v>37000</v>
       </c>
       <c r="J60" s="3">
         <v>35900</v>
@@ -2667,10 +2667,10 @@
         <v>3600</v>
       </c>
       <c r="H61" s="3">
-        <v>2100</v>
+        <v>3700</v>
       </c>
       <c r="I61" s="3">
-        <v>2100</v>
+        <v>3700</v>
       </c>
       <c r="J61" s="3">
         <v>800</v>
@@ -2872,10 +2872,10 @@
         <v>41400</v>
       </c>
       <c r="H66" s="3">
-        <v>30700</v>
+        <v>40900</v>
       </c>
       <c r="I66" s="3">
-        <v>30700</v>
+        <v>40900</v>
       </c>
       <c r="J66" s="3">
         <v>36700</v>
@@ -3094,10 +3094,10 @@
         <v>2100</v>
       </c>
       <c r="H72" s="3">
-        <v>1800</v>
+        <v>4900</v>
       </c>
       <c r="I72" s="3">
-        <v>1800</v>
+        <v>4900</v>
       </c>
       <c r="J72" s="3">
         <v>1600</v>
@@ -3258,10 +3258,10 @@
         <v>11200</v>
       </c>
       <c r="H76" s="3">
-        <v>8900</v>
+        <v>4900</v>
       </c>
       <c r="I76" s="3">
-        <v>8900</v>
+        <v>4900</v>
       </c>
       <c r="J76" s="3">
         <v>2700</v>
@@ -3386,10 +3386,10 @@
         <v>100</v>
       </c>
       <c r="H81" s="3">
-        <v>-800</v>
+        <v>-700</v>
       </c>
       <c r="I81" s="3">
-        <v>-800</v>
+        <v>-700</v>
       </c>
       <c r="J81" s="3">
         <v>800</v>
@@ -3444,7 +3444,7 @@
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3">
         <v>200</v>
@@ -3690,10 +3690,10 @@
         <v>-200</v>
       </c>
       <c r="H89" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="I89" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="J89" s="3">
         <v>600</v>
@@ -4175,10 +4175,10 @@
         <v>200</v>
       </c>
       <c r="H102" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I102" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J102" s="3">
         <v>100</v>
